--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/MINNESOTA_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/MINNESOTA_2011.xlsx
@@ -2706,7 +2706,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C131">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C483">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C535">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C761">
@@ -15666,7 +15666,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C851">
